--- a/human_resources_forms/024_staff_certification_assessment--human_resources_forms.xlsx
+++ b/human_resources_forms/024_staff_certification_assessment--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_'2.1.1',_'label':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': '2.1.1', 'label': 'High School'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_'2.1.2',_'label':_'some_college'}</t>
+          <t>some_college</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': '2.1.2', 'label': 'Some College'}</t>
+          <t>Some College</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'2.1.3',_'label':_"bachelor's"}</t>
+          <t>bachelor's</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': '2.1.3', 'label': "Bachelor's"}</t>
+          <t>Bachelor's</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'2.1.4',_'label':_"master's"}</t>
+          <t>master's</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': '2.1.4', 'label': "Master's"}</t>
+          <t>Master's</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'2.1.5',_'label':_'doctoral'}</t>
+          <t>doctoral</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': '2.1.5', 'label': 'Doctoral'}</t>
+          <t>Doctoral</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'3.1.1',_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': '3.1.1', 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_'3.1.2',_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': '3.1.2', 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_'5.1.1',_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': '5.1.1', 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_'5.1.2',_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': '5.1.2', 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_'6.1.1',_'label':_'peer_evaluation'}</t>
+          <t>peer_evaluation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': '6.1.1', 'label': 'Peer Evaluation'}</t>
+          <t>Peer Evaluation</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_'6.1.2',_'label':_'managerial_evaluation'}</t>
+          <t>managerial_evaluation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': '6.1.2', 'label': 'Managerial Evaluation'}</t>
+          <t>Managerial Evaluation</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_'6.1.3',_'label':_'self-evaluation'}</t>
+          <t>self-evaluation</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': '6.1.3', 'label': 'Self-Evaluation'}</t>
+          <t>Self-Evaluation</t>
         </is>
       </c>
     </row>
